--- a/packages/templates/files/sheet-todo.xlsx
+++ b/packages/templates/files/sheet-todo.xlsx
@@ -328,7 +328,7 @@
       </c>
       <c r="C5" s="4">
         <f>TODAY()+2</f>
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -359,7 +359,7 @@
       </c>
       <c r="C6" s="4">
         <f>TODAY()+5</f>
-        <v>46313</v>
+        <v>46320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -390,7 +390,7 @@
       </c>
       <c r="C7" s="4">
         <f>TODAY()+9</f>
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -416,7 +416,7 @@
       </c>
       <c r="C8" s="4">
         <f>TODAY()+12</f>
-        <v>46320</v>
+        <v>46327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -447,7 +447,7 @@
       </c>
       <c r="C9" s="4">
         <f>TODAY()+14</f>
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -473,7 +473,7 @@
       </c>
       <c r="C10" s="4">
         <f>TODAY()+16</f>
-        <v>46324</v>
+        <v>46331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
